--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1002,6 +1002,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1011,7 +1014,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1323,6 +1326,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>208000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>210000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1365,7 +1371,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1677,6 +1683,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1686,7 +1695,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1998,6 +2007,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>388822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>416560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2040,7 +2052,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2352,6 +2364,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2361,7 +2376,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2673,6 +2688,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>180822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>206560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2694,11 +2712,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="474834816"/>
-        <c:axId val="474836352"/>
+        <c:axId val="595687680"/>
+        <c:axId val="621724032"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="474834816"/>
+        <c:axId val="595687680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2738,14 +2756,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474836352"/>
+        <c:crossAx val="621724032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="474836352"/>
+        <c:axId val="621724032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2794,7 +2812,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474834816"/>
+        <c:crossAx val="595687680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2924,7 +2942,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3236,6 +3254,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3245,7 +3266,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3557,6 +3578,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>208000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>210000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3590,7 +3614,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3902,6 +3926,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3911,7 +3938,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4223,6 +4250,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>388822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>416560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4256,7 +4286,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4568,6 +4598,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4577,7 +4610,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4889,6 +4922,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>180822.75954229012</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>206560.05776522681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4910,11 +4946,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="507685504"/>
-        <c:axId val="510284160"/>
+        <c:axId val="559166976"/>
+        <c:axId val="559168512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="507685504"/>
+        <c:axId val="559166976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4924,14 +4960,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="510284160"/>
+        <c:crossAx val="559168512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="510284160"/>
+        <c:axId val="559168512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4942,7 +4978,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="507685504"/>
+        <c:crossAx val="559166976"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5060,7 +5096,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5372,6 +5408,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5381,7 +5420,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5693,6 +5732,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5735,7 +5777,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6047,6 +6089,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6056,7 +6101,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6368,6 +6413,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>406964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>435902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6410,7 +6458,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6722,6 +6770,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6731,7 +6782,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7043,6 +7094,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>191964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>218902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7064,11 +7118,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="536818432"/>
-        <c:axId val="536819968"/>
+        <c:axId val="559819008"/>
+        <c:axId val="559828992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="536818432"/>
+        <c:axId val="559819008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7108,14 +7162,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536819968"/>
+        <c:crossAx val="559828992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="536819968"/>
+        <c:axId val="559828992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7164,7 +7218,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="536818432"/>
+        <c:crossAx val="559819008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7294,7 +7348,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7606,6 +7660,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7615,7 +7672,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7927,6 +7984,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7960,7 +8020,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8272,6 +8332,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8281,7 +8344,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8593,6 +8656,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>406964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>435902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8626,7 +8692,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8938,6 +9004,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8947,7 +9016,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9259,6 +9328,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>191964.33522915788</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>218902.47659264668</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9280,11 +9352,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426576512"/>
-        <c:axId val="426582400"/>
+        <c:axId val="559844352"/>
+        <c:axId val="559846144"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426576512"/>
+        <c:axId val="559844352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9294,14 +9366,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426582400"/>
+        <c:crossAx val="559846144"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426582400"/>
+        <c:axId val="559846144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9312,7 +9384,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426576512"/>
+        <c:crossAx val="559844352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9430,7 +9502,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9742,6 +9814,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9751,7 +9826,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10063,6 +10138,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10105,7 +10183,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10417,6 +10495,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10426,7 +10507,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10738,6 +10819,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>405615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>434464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10780,7 +10864,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11092,6 +11176,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11101,7 +11188,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11413,6 +11500,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>190615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11434,11 +11524,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426852352"/>
-        <c:axId val="426853888"/>
+        <c:axId val="559923200"/>
+        <c:axId val="559924736"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426852352"/>
+        <c:axId val="559923200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11478,14 +11568,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426853888"/>
+        <c:crossAx val="559924736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426853888"/>
+        <c:axId val="559924736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11534,7 +11624,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="426852352"/>
+        <c:crossAx val="559923200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11664,7 +11754,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11976,6 +12066,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11985,7 +12078,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12297,6 +12390,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>215000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12330,7 +12426,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12642,6 +12738,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12651,7 +12750,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12963,6 +13062,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>405615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>434464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12996,7 +13098,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13308,6 +13410,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13317,7 +13422,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="104"/>
+                <c:ptCount val="105"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13629,6 +13734,9 @@
                 </c:pt>
                 <c:pt idx="103">
                   <c:v>190615.31121444347</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>217464.15679335035</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13650,11 +13758,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="426869120"/>
-        <c:axId val="426870656"/>
+        <c:axId val="560140288"/>
+        <c:axId val="560141824"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="426869120"/>
+        <c:axId val="560140288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13664,14 +13772,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426870656"/>
+        <c:crossAx val="560141824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="426870656"/>
+        <c:axId val="560141824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13682,7 +13790,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="426869120"/>
+        <c:crossAx val="560140288"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14209,7 +14317,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB106"/>
+  <dimension ref="A1:AB107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -17989,6 +18097,35 @@
         <v>180822.75954229012</v>
       </c>
     </row>
+    <row r="107" spans="1:9" ht="12.75">
+      <c r="A107" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B107" s="18">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C107" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="15">
+        <v>833.33330021964309</v>
+      </c>
+      <c r="E107" s="15">
+        <v>173566.6838385908</v>
+      </c>
+      <c r="F107" s="15">
+        <v>416560.05776522681</v>
+      </c>
+      <c r="G107" s="15">
+        <v>210000</v>
+      </c>
+      <c r="H107" s="15">
+        <v>416560.05776522681</v>
+      </c>
+      <c r="I107" s="15">
+        <v>206560.05776522681</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18000,7 +18137,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH106"/>
+  <dimension ref="A1:AH107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23407,6 +23544,50 @@
         <v>63.365781700810651</v>
       </c>
     </row>
+    <row r="107" spans="1:14" ht="12.75">
+      <c r="A107" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B107" s="18">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C107" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="15">
+        <v>833.33330021964309</v>
+      </c>
+      <c r="E107" s="15">
+        <v>181626.02469643299</v>
+      </c>
+      <c r="F107" s="15">
+        <v>435902.47659264668</v>
+      </c>
+      <c r="G107" s="15">
+        <v>217000</v>
+      </c>
+      <c r="H107" s="15">
+        <v>435902.47659264668</v>
+      </c>
+      <c r="I107" s="15">
+        <v>218902.47659264668</v>
+      </c>
+      <c r="J107" s="21">
+        <v>0.14900016784667969</v>
+      </c>
+      <c r="K107" s="21">
+        <v>0.14010746704699642</v>
+      </c>
+      <c r="L107" s="21">
+        <v>0.14900016784667969</v>
+      </c>
+      <c r="M107" s="23">
+        <v>0.20675190258530632</v>
+      </c>
+      <c r="N107" s="21">
+        <v>67.765986815617211</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23418,7 +23599,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH106"/>
+  <dimension ref="A1:AH107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -29648,6 +29829,59 @@
         <v>64.562273357270726</v>
       </c>
     </row>
+    <row r="107" spans="1:17" ht="12.75">
+      <c r="A107" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B107" s="18">
+        <v>2.4000000953674316</v>
+      </c>
+      <c r="C107" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="15">
+        <v>833.33330021964309</v>
+      </c>
+      <c r="E107" s="15">
+        <v>181026.72480387357</v>
+      </c>
+      <c r="F107" s="15">
+        <v>434464.15679335035</v>
+      </c>
+      <c r="G107" s="15">
+        <v>217000</v>
+      </c>
+      <c r="H107" s="15">
+        <v>434464.15679335035</v>
+      </c>
+      <c r="I107" s="15">
+        <v>217464.15679335035</v>
+      </c>
+      <c r="J107" s="15">
+        <v>2.4330000877380371</v>
+      </c>
+      <c r="K107" s="15">
+        <v>2.2260000705718994</v>
+      </c>
+      <c r="L107" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M107" s="19">
+        <v>1.2999999523162842</v>
+      </c>
+      <c r="N107" s="21">
+        <v>71.942453334905125</v>
+      </c>
+      <c r="O107" s="21">
+        <v>70.756255946162113</v>
+      </c>
+      <c r="P107" s="21">
+        <v>72.227818114754385</v>
+      </c>
+      <c r="Q107" s="21">
+        <v>67.813131608977557</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1005,6 +1005,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1014,7 +1017,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1329,6 +1332,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>212000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1371,7 +1377,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1686,6 +1692,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1695,7 +1704,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2010,6 +2019,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>416560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>453620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2052,7 +2064,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2367,6 +2379,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2376,7 +2391,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2691,6 +2706,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>206560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>241620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2712,11 +2730,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595687680"/>
-        <c:axId val="621724032"/>
+        <c:axId val="559776512"/>
+        <c:axId val="559778048"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595687680"/>
+        <c:axId val="559776512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2756,14 +2774,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="621724032"/>
+        <c:crossAx val="559778048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="621724032"/>
+        <c:axId val="559778048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2812,7 +2830,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595687680"/>
+        <c:crossAx val="559776512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2942,7 +2960,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3257,6 +3275,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3266,7 +3287,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3581,6 +3602,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>210000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>212000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3614,7 +3638,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3929,6 +3953,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3938,7 +3965,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4253,6 +4280,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>416560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>453620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4286,7 +4316,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4601,6 +4631,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4610,7 +4643,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4925,6 +4958,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>206560.05776522681</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>241620.51101696113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4946,11 +4982,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559166976"/>
-        <c:axId val="559168512"/>
+        <c:axId val="662115072"/>
+        <c:axId val="662116608"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559166976"/>
+        <c:axId val="662115072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4960,14 +4996,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559168512"/>
+        <c:crossAx val="662116608"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559168512"/>
+        <c:axId val="662116608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4978,7 +5014,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559166976"/>
+        <c:crossAx val="662115072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5096,7 +5132,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5411,6 +5447,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5420,7 +5459,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5735,6 +5774,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5777,7 +5819,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6092,6 +6134,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6101,7 +6146,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6416,6 +6461,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>435902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>474590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6458,7 +6506,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6773,6 +6821,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6782,7 +6833,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7097,6 +7148,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>218902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>255590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7118,11 +7172,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559819008"/>
-        <c:axId val="559828992"/>
+        <c:axId val="662022016"/>
+        <c:axId val="662023552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559819008"/>
+        <c:axId val="662022016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7162,14 +7216,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559828992"/>
+        <c:crossAx val="662023552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559828992"/>
+        <c:axId val="662023552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7218,7 +7272,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559819008"/>
+        <c:crossAx val="662022016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7348,7 +7402,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7663,6 +7717,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7672,7 +7729,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -7987,6 +8044,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8020,7 +8080,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8335,6 +8395,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8344,7 +8407,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8659,6 +8722,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>435902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>474590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8692,7 +8758,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9007,6 +9073,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9016,7 +9085,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9331,6 +9400,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>218902.47659264668</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>255590.91591369454</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9352,11 +9424,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559844352"/>
-        <c:axId val="559846144"/>
+        <c:axId val="662067456"/>
+        <c:axId val="662069248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559844352"/>
+        <c:axId val="662067456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9366,14 +9438,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559846144"/>
+        <c:crossAx val="662069248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559846144"/>
+        <c:axId val="662069248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9384,7 +9456,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="559844352"/>
+        <c:crossAx val="662067456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9502,7 +9574,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9817,6 +9889,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9826,7 +9901,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10141,6 +10216,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10183,7 +10261,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10498,6 +10576,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10507,7 +10588,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10822,6 +10903,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>434464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>473031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10864,7 +10948,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11179,6 +11263,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11188,7 +11275,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11503,6 +11590,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>254031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11524,11 +11614,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559923200"/>
-        <c:axId val="559924736"/>
+        <c:axId val="662129664"/>
+        <c:axId val="662135552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559923200"/>
+        <c:axId val="662129664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11568,14 +11658,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559924736"/>
+        <c:crossAx val="662135552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559924736"/>
+        <c:axId val="662135552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11624,7 +11714,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559923200"/>
+        <c:crossAx val="662129664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11754,7 +11844,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12069,6 +12159,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12078,7 +12171,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12393,6 +12486,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>219000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12426,7 +12522,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12741,6 +12837,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12750,7 +12849,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13065,6 +13164,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>434464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>473031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13098,7 +13200,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13413,6 +13515,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13422,7 +13527,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13737,6 +13842,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>217464.15679335035</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>254031.53759439802</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13758,11 +13866,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="560140288"/>
-        <c:axId val="560141824"/>
+        <c:axId val="662150528"/>
+        <c:axId val="662160512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="560140288"/>
+        <c:axId val="662150528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13772,14 +13880,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="560141824"/>
+        <c:crossAx val="662160512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="560141824"/>
+        <c:axId val="662160512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13790,7 +13898,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="560140288"/>
+        <c:crossAx val="662150528"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13832,7 +13940,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13870,7 +13978,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13911,7 +14019,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13949,7 +14057,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13992,7 +14100,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14030,7 +14138,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14308,7 +14416,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14317,7 +14425,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB107"/>
+  <dimension ref="A1:AB108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18126,6 +18234,35 @@
         <v>206560.05776522681</v>
       </c>
     </row>
+    <row r="108" spans="1:9" ht="12.75">
+      <c r="A108" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B108" s="18">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C108" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="15">
+        <v>768.63950863415198</v>
+      </c>
+      <c r="E108" s="15">
+        <v>174335.32334722497</v>
+      </c>
+      <c r="F108" s="15">
+        <v>453620.51101696113</v>
+      </c>
+      <c r="G108" s="15">
+        <v>212000</v>
+      </c>
+      <c r="H108" s="15">
+        <v>453620.51101696113</v>
+      </c>
+      <c r="I108" s="15">
+        <v>241620.51101696113</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18137,7 +18274,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23588,6 +23725,50 @@
         <v>67.765986815617211</v>
       </c>
     </row>
+    <row r="108" spans="1:14" ht="12.75">
+      <c r="A108" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B108" s="18">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C108" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="15">
+        <v>768.63950863415198</v>
+      </c>
+      <c r="E108" s="15">
+        <v>182394.66420506715</v>
+      </c>
+      <c r="F108" s="15">
+        <v>474590.91591369454</v>
+      </c>
+      <c r="G108" s="15">
+        <v>219000</v>
+      </c>
+      <c r="H108" s="15">
+        <v>474590.91591369454</v>
+      </c>
+      <c r="I108" s="15">
+        <v>255590.91591369454</v>
+      </c>
+      <c r="J108" s="21">
+        <v>0.20199990272521973</v>
+      </c>
+      <c r="K108" s="21">
+        <v>0.15042287299336696</v>
+      </c>
+      <c r="L108" s="21">
+        <v>0.20199990272521973</v>
+      </c>
+      <c r="M108" s="23">
+        <v>0.20595990260862521</v>
+      </c>
+      <c r="N108" s="21">
+        <v>73.035028220618088</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23599,7 +23780,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH107"/>
+  <dimension ref="A1:AH108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -29882,6 +30063,59 @@
         <v>67.813131608977557</v>
       </c>
     </row>
+    <row r="108" spans="1:17" ht="12.75">
+      <c r="A108" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B108" s="18">
+        <v>2.6019999980926514</v>
+      </c>
+      <c r="C108" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D108" s="15">
+        <v>768.63950863415198</v>
+      </c>
+      <c r="E108" s="15">
+        <v>181795.36431250774</v>
+      </c>
+      <c r="F108" s="15">
+        <v>473031.53759439802</v>
+      </c>
+      <c r="G108" s="15">
+        <v>219000</v>
+      </c>
+      <c r="H108" s="15">
+        <v>473031.53759439802</v>
+      </c>
+      <c r="I108" s="15">
+        <v>254031.53759439802</v>
+      </c>
+      <c r="J108" s="15">
+        <v>2.684999942779541</v>
+      </c>
+      <c r="K108" s="15">
+        <v>2.4119999408721924</v>
+      </c>
+      <c r="L108" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M108" s="19">
+        <v>1.4229999780654907</v>
+      </c>
+      <c r="N108" s="21">
+        <v>83.854907882845595</v>
+      </c>
+      <c r="O108" s="21">
+        <v>75.122473258389945</v>
+      </c>
+      <c r="P108" s="21">
+        <v>73.192703162632895</v>
+      </c>
+      <c r="Q108" s="21">
+        <v>78.982013449904031</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1008,6 +1008,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1017,7 +1020,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1335,6 +1338,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>212000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>214000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1377,7 +1383,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1695,6 +1701,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1704,7 +1713,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2022,6 +2031,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>453620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>442022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2064,7 +2076,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2382,6 +2394,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2391,7 +2406,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2709,6 +2724,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>241620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>228022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2730,11 +2748,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559776512"/>
-        <c:axId val="559778048"/>
+        <c:axId val="396994432"/>
+        <c:axId val="397587200"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559776512"/>
+        <c:axId val="396994432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2774,14 +2792,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559778048"/>
+        <c:crossAx val="397587200"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559778048"/>
+        <c:axId val="397587200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2830,7 +2848,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559776512"/>
+        <c:crossAx val="396994432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2960,7 +2978,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3278,6 +3296,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3287,7 +3308,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3605,6 +3626,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>212000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>214000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3638,7 +3662,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3956,6 +3980,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3965,7 +3992,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4283,6 +4310,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>453620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>442022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4316,7 +4346,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4634,6 +4664,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4643,7 +4676,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4961,6 +4994,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>241620.51101696113</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>228022.34382522095</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4982,11 +5018,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662115072"/>
-        <c:axId val="662116608"/>
+        <c:axId val="483329920"/>
+        <c:axId val="483409920"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662115072"/>
+        <c:axId val="483329920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4996,14 +5032,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662116608"/>
+        <c:crossAx val="483409920"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662116608"/>
+        <c:axId val="483409920"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5014,7 +5050,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662115072"/>
+        <c:crossAx val="483329920"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5132,7 +5168,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5450,6 +5486,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5459,7 +5498,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5777,6 +5816,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5819,7 +5861,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6137,6 +6179,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6146,7 +6191,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6464,6 +6509,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>474590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>462364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6506,7 +6554,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6824,6 +6872,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6833,7 +6884,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7151,6 +7202,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>255590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>241364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7172,11 +7226,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662022016"/>
-        <c:axId val="662023552"/>
+        <c:axId val="543747456"/>
+        <c:axId val="623974272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662022016"/>
+        <c:axId val="543747456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7216,14 +7270,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662023552"/>
+        <c:crossAx val="623974272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662023552"/>
+        <c:axId val="623974272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7272,7 +7326,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662022016"/>
+        <c:crossAx val="543747456"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7402,7 +7456,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7720,6 +7774,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7729,7 +7786,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8047,6 +8104,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8080,7 +8140,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8398,6 +8458,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8407,7 +8470,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8725,6 +8788,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>474590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>462364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8758,7 +8824,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9076,6 +9142,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9085,7 +9154,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9403,6 +9472,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>255590.91591369454</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>241364.11958165164</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9424,11 +9496,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662067456"/>
-        <c:axId val="662069248"/>
+        <c:axId val="533193856"/>
+        <c:axId val="533195392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662067456"/>
+        <c:axId val="533193856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9438,14 +9510,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662069248"/>
+        <c:crossAx val="533195392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662069248"/>
+        <c:axId val="533195392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9456,7 +9528,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662067456"/>
+        <c:crossAx val="533193856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9574,7 +9646,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9892,6 +9964,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9901,7 +9976,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10219,6 +10294,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10261,7 +10339,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10579,6 +10657,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10588,7 +10669,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10906,6 +10987,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>473031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>460851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10948,7 +11032,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11266,6 +11350,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11275,7 +11362,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11593,6 +11680,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>254031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>239851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11614,11 +11704,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662129664"/>
-        <c:axId val="662135552"/>
+        <c:axId val="535725952"/>
+        <c:axId val="535727488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662129664"/>
+        <c:axId val="535725952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11658,14 +11748,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662135552"/>
+        <c:crossAx val="535727488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662135552"/>
+        <c:axId val="535727488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11714,7 +11804,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662129664"/>
+        <c:crossAx val="535725952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11844,7 +11934,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12162,6 +12252,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12171,7 +12264,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12489,6 +12582,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>219000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>221000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12522,7 +12618,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12840,6 +12936,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12849,7 +12948,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13167,6 +13266,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>473031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>460851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13200,7 +13302,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13518,6 +13620,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13527,7 +13632,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13845,6 +13950,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>254031.53759439802</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>239851.48669512541</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13866,11 +13974,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662150528"/>
-        <c:axId val="662160512"/>
+        <c:axId val="535755008"/>
+        <c:axId val="535830528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662150528"/>
+        <c:axId val="535755008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13880,14 +13988,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662160512"/>
+        <c:crossAx val="535830528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="662160512"/>
+        <c:axId val="535830528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13898,7 +14006,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="662150528"/>
+        <c:crossAx val="535755008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13940,7 +14048,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -13978,7 +14086,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14019,7 +14127,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14057,7 +14165,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14100,7 +14208,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14138,7 +14246,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14416,7 +14524,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14425,7 +14533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB108"/>
+  <dimension ref="A1:AB109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18263,6 +18371,35 @@
         <v>241620.51101696113</v>
       </c>
     </row>
+    <row r="109" spans="1:9" ht="12.75">
+      <c r="A109" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B109" s="18">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C109" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="15">
+        <v>792.39304909694238</v>
+      </c>
+      <c r="E109" s="15">
+        <v>175127.71639632192</v>
+      </c>
+      <c r="F109" s="15">
+        <v>442022.34382522095</v>
+      </c>
+      <c r="G109" s="15">
+        <v>214000</v>
+      </c>
+      <c r="H109" s="15">
+        <v>442022.34382522095</v>
+      </c>
+      <c r="I109" s="15">
+        <v>228022.34382522095</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18274,7 +18411,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23769,6 +23906,50 @@
         <v>73.035028220618088</v>
       </c>
     </row>
+    <row r="109" spans="1:14" ht="12.75">
+      <c r="A109" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B109" s="18">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C109" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="15">
+        <v>792.39304909694238</v>
+      </c>
+      <c r="E109" s="15">
+        <v>183187.0572541641</v>
+      </c>
+      <c r="F109" s="15">
+        <v>462364.11958165164</v>
+      </c>
+      <c r="G109" s="15">
+        <v>221000</v>
+      </c>
+      <c r="H109" s="15">
+        <v>462364.11958165164</v>
+      </c>
+      <c r="I109" s="15">
+        <v>241364.11958165164</v>
+      </c>
+      <c r="J109" s="21">
+        <v>0</v>
+      </c>
+      <c r="K109" s="21">
+        <v>0.12535239416113914</v>
+      </c>
+      <c r="L109" s="21">
+        <v>7.8000068664550781E-2</v>
+      </c>
+      <c r="M109" s="23">
+        <v>0.18463326361794616</v>
+      </c>
+      <c r="N109" s="21">
+        <v>67.892638468724456</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23780,7 +23961,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH108"/>
+  <dimension ref="A1:AH109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -30116,6 +30297,59 @@
         <v>78.982013449904031</v>
       </c>
     </row>
+    <row r="109" spans="1:17" ht="12.75">
+      <c r="A109" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B109" s="18">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="C109" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D109" s="15">
+        <v>792.39304909694238</v>
+      </c>
+      <c r="E109" s="15">
+        <v>182587.75736160469</v>
+      </c>
+      <c r="F109" s="15">
+        <v>460851.48669512541</v>
+      </c>
+      <c r="G109" s="15">
+        <v>221000</v>
+      </c>
+      <c r="H109" s="15">
+        <v>460851.48669512541</v>
+      </c>
+      <c r="I109" s="15">
+        <v>239851.48669512541</v>
+      </c>
+      <c r="J109" s="15">
+        <v>2.6319999694824219</v>
+      </c>
+      <c r="K109" s="15">
+        <v>2.3610000610351562</v>
+      </c>
+      <c r="L109" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M109" s="19">
+        <v>1.4299999475479126</v>
+      </c>
+      <c r="N109" s="21">
+        <v>78.198709352850372</v>
+      </c>
+      <c r="O109" s="21">
+        <v>76.147885289876754</v>
+      </c>
+      <c r="P109" s="21">
+        <v>74.177763871714191</v>
+      </c>
+      <c r="Q109" s="21">
+        <v>80.088128126201894</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1011,6 +1011,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1020,7 +1023,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1341,6 +1344,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>214000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>216000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1383,7 +1389,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1704,6 +1710,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1713,7 +1722,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2034,6 +2043,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>442022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>399014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2076,7 +2088,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2397,6 +2409,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2406,7 +2421,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2727,6 +2742,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>228022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>183014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2748,11 +2766,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="396994432"/>
-        <c:axId val="397587200"/>
+        <c:axId val="521324032"/>
+        <c:axId val="521325568"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="396994432"/>
+        <c:axId val="521324032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2792,14 +2810,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397587200"/>
+        <c:crossAx val="521325568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="397587200"/>
+        <c:axId val="521325568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2848,7 +2866,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="396994432"/>
+        <c:crossAx val="521324032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2978,7 +2996,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3299,6 +3317,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3308,7 +3329,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3629,6 +3650,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>214000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>216000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3662,7 +3686,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3983,6 +4007,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3992,7 +4019,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4313,6 +4340,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>442022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>399014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4346,7 +4376,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4667,6 +4697,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4676,7 +4709,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4997,6 +5030,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>228022.34382522095</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>183014.52605583996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5018,11 +5054,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="483329920"/>
-        <c:axId val="483409920"/>
+        <c:axId val="401282944"/>
+        <c:axId val="401284480"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="483329920"/>
+        <c:axId val="401282944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5032,14 +5068,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="483409920"/>
+        <c:crossAx val="401284480"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="483409920"/>
+        <c:axId val="401284480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5050,7 +5086,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="483329920"/>
+        <c:crossAx val="401282944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5168,7 +5204,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5489,6 +5525,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5498,7 +5537,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5819,6 +5858,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5861,7 +5903,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6182,6 +6224,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6191,7 +6236,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6512,6 +6557,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>462364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>417285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6554,7 +6602,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6875,6 +6923,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6884,7 +6935,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7205,6 +7256,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>241364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>194285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7226,11 +7280,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="543747456"/>
-        <c:axId val="623974272"/>
+        <c:axId val="401312384"/>
+        <c:axId val="401318272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="543747456"/>
+        <c:axId val="401312384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7270,14 +7324,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="623974272"/>
+        <c:crossAx val="401318272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="623974272"/>
+        <c:axId val="401318272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7326,7 +7380,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543747456"/>
+        <c:crossAx val="401312384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7456,7 +7510,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7777,6 +7831,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7786,7 +7843,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8107,6 +8164,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8140,7 +8200,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8461,6 +8521,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8470,7 +8533,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8791,6 +8854,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>462364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>417285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8824,7 +8890,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9145,6 +9211,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9154,7 +9223,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9475,6 +9544,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>241364.11958165164</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>194285.05145775672</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9496,11 +9568,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="533193856"/>
-        <c:axId val="533195392"/>
+        <c:axId val="401337728"/>
+        <c:axId val="395383936"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="533193856"/>
+        <c:axId val="401337728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9510,14 +9582,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="533195392"/>
+        <c:crossAx val="395383936"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533195392"/>
+        <c:axId val="395383936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9528,7 +9600,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="533193856"/>
+        <c:crossAx val="401337728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9646,7 +9718,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9967,6 +10039,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9976,7 +10051,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10297,6 +10372,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10339,7 +10417,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10660,6 +10738,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10669,7 +10750,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10990,6 +11071,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>460851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>415926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11032,7 +11116,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11353,6 +11437,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11362,7 +11449,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11683,6 +11770,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>239851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>192926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11704,11 +11794,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="535725952"/>
-        <c:axId val="535727488"/>
+        <c:axId val="419365248"/>
+        <c:axId val="419366784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="535725952"/>
+        <c:axId val="419365248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11748,14 +11838,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535727488"/>
+        <c:crossAx val="419366784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535727488"/>
+        <c:axId val="419366784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11804,7 +11894,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535725952"/>
+        <c:crossAx val="419365248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11934,7 +12024,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12255,6 +12345,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12264,7 +12357,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12585,6 +12678,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>221000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>223000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12618,7 +12714,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12939,6 +13035,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12948,7 +13047,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13269,6 +13368,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>460851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>415926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13302,7 +13404,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13623,6 +13725,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13632,7 +13737,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13953,6 +14058,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>239851.48669512541</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>192926.43862532912</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13974,11 +14082,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="535755008"/>
-        <c:axId val="535830528"/>
+        <c:axId val="419390208"/>
+        <c:axId val="419391744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="535755008"/>
+        <c:axId val="419390208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13988,14 +14096,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="535830528"/>
+        <c:crossAx val="419391744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535830528"/>
+        <c:axId val="419391744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14006,7 +14114,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="535755008"/>
+        <c:crossAx val="419390208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14048,7 +14156,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14086,7 +14194,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14127,7 +14235,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14165,7 +14273,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14208,7 +14316,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14246,7 +14354,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14524,7 +14632,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14533,7 +14641,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB109"/>
+  <dimension ref="A1:AB110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18400,6 +18508,35 @@
         <v>228022.34382522095</v>
       </c>
     </row>
+    <row r="110" spans="1:9" ht="12.75">
+      <c r="A110" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="18">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C110" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="15">
+        <v>882.22321805772049</v>
+      </c>
+      <c r="E110" s="15">
+        <v>176009.93961437963</v>
+      </c>
+      <c r="F110" s="15">
+        <v>399014.52605583996</v>
+      </c>
+      <c r="G110" s="15">
+        <v>216000</v>
+      </c>
+      <c r="H110" s="15">
+        <v>399014.52605583996</v>
+      </c>
+      <c r="I110" s="15">
+        <v>183014.52605583996</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18411,7 +18548,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -23950,6 +24087,50 @@
         <v>67.892638468724456</v>
       </c>
     </row>
+    <row r="110" spans="1:14" ht="12.75">
+      <c r="A110" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="18">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C110" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="15">
+        <v>882.22321805772049</v>
+      </c>
+      <c r="E110" s="15">
+        <v>184069.28047222181</v>
+      </c>
+      <c r="F110" s="15">
+        <v>417285.05145775672</v>
+      </c>
+      <c r="G110" s="15">
+        <v>223000</v>
+      </c>
+      <c r="H110" s="15">
+        <v>417285.05145775672</v>
+      </c>
+      <c r="I110" s="15">
+        <v>194285.05145775672</v>
+      </c>
+      <c r="J110" s="21">
+        <v>0</v>
+      </c>
+      <c r="K110" s="21">
+        <v>0.10446032846761595</v>
+      </c>
+      <c r="L110" s="21">
+        <v>0.25699996948242188</v>
+      </c>
+      <c r="M110" s="23">
+        <v>0.19669438126202543</v>
+      </c>
+      <c r="N110" s="21">
+        <v>53.107937195450262</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23961,7 +24142,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH109"/>
+  <dimension ref="A1:AH110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -30350,6 +30531,59 @@
         <v>80.088128126201894</v>
       </c>
     </row>
+    <row r="110" spans="1:17" ht="12.75">
+      <c r="A110" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="18">
+        <v>2.2669999599456787</v>
+      </c>
+      <c r="C110" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D110" s="15">
+        <v>882.22321805772049</v>
+      </c>
+      <c r="E110" s="15">
+        <v>183469.9805796624</v>
+      </c>
+      <c r="F110" s="15">
+        <v>415926.43862532912</v>
+      </c>
+      <c r="G110" s="15">
+        <v>223000</v>
+      </c>
+      <c r="H110" s="15">
+        <v>415926.43862532912</v>
+      </c>
+      <c r="I110" s="15">
+        <v>192926.43862532912</v>
+      </c>
+      <c r="J110" s="15">
+        <v>2.5239999294281006</v>
+      </c>
+      <c r="K110" s="15">
+        <v>2.25</v>
+      </c>
+      <c r="L110" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M110" s="19">
+        <v>1.4939999580383301</v>
+      </c>
+      <c r="N110" s="21">
+        <v>57.902620211179922</v>
+      </c>
+      <c r="O110" s="21">
+        <v>70.066130263644482</v>
+      </c>
+      <c r="P110" s="21">
+        <v>72.807219335690959</v>
+      </c>
+      <c r="Q110" s="21">
+        <v>64.583952119551526</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1014,6 +1014,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1023,7 +1026,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1347,6 +1350,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>216000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>218000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1389,7 +1395,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1713,6 +1719,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1722,7 +1731,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2046,6 +2055,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>399014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>493067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2088,7 +2100,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2412,6 +2424,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2421,7 +2436,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2745,6 +2760,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>183014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>275067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2766,11 +2784,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521324032"/>
-        <c:axId val="521325568"/>
+        <c:axId val="578683264"/>
+        <c:axId val="578684800"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521324032"/>
+        <c:axId val="578683264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2810,14 +2828,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521325568"/>
+        <c:crossAx val="578684800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="521325568"/>
+        <c:axId val="578684800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2866,7 +2884,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521324032"/>
+        <c:crossAx val="578683264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2996,7 +3014,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3320,6 +3338,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3329,7 +3350,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3653,6 +3674,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>216000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>218000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3686,7 +3710,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4010,6 +4034,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4019,7 +4046,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4343,6 +4370,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>399014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>493067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4376,7 +4406,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4700,6 +4730,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4709,7 +4742,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5033,6 +5066,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>183014.52605583996</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>275067.72480987286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5054,11 +5090,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401282944"/>
-        <c:axId val="401284480"/>
+        <c:axId val="578708224"/>
+        <c:axId val="578709760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401282944"/>
+        <c:axId val="578708224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5068,14 +5104,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="401284480"/>
+        <c:crossAx val="578709760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401284480"/>
+        <c:axId val="578709760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5086,7 +5122,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="401282944"/>
+        <c:crossAx val="578708224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5204,7 +5240,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5528,6 +5564,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5537,7 +5576,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5861,6 +5900,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5903,7 +5945,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6227,6 +6269,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6236,7 +6281,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6560,6 +6605,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>417285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>515553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6602,7 +6650,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6926,6 +6974,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6935,7 +6986,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7259,6 +7310,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>194285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>290553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7280,11 +7334,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401312384"/>
-        <c:axId val="401318272"/>
+        <c:axId val="578741760"/>
+        <c:axId val="578743296"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401312384"/>
+        <c:axId val="578741760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7324,14 +7378,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401318272"/>
+        <c:crossAx val="578743296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="401318272"/>
+        <c:axId val="578743296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7380,7 +7434,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401312384"/>
+        <c:crossAx val="578741760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7510,7 +7564,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7834,6 +7888,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7843,7 +7900,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8167,6 +8224,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8200,7 +8260,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8524,6 +8584,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8533,7 +8596,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8857,6 +8920,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>417285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>515553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8890,7 +8956,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9214,6 +9280,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9223,7 +9292,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9547,6 +9616,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>194285.05145775672</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>290553.28549581306</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9568,11 +9640,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401337728"/>
-        <c:axId val="395383936"/>
+        <c:axId val="638392576"/>
+        <c:axId val="638398464"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401337728"/>
+        <c:axId val="638392576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9582,14 +9654,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="395383936"/>
+        <c:crossAx val="638398464"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395383936"/>
+        <c:axId val="638398464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9600,7 +9672,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="401337728"/>
+        <c:crossAx val="638392576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9718,7 +9790,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10042,6 +10114,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10051,7 +10126,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10375,6 +10450,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10417,7 +10495,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10741,6 +10819,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10750,7 +10831,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11074,6 +11155,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>415926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>513881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11116,7 +11200,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11440,6 +11524,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11449,7 +11536,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11773,6 +11860,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>192926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>288881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11794,11 +11884,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="419365248"/>
-        <c:axId val="419366784"/>
+        <c:axId val="638802944"/>
+        <c:axId val="638808832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="419365248"/>
+        <c:axId val="638802944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11838,14 +11928,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="419366784"/>
+        <c:crossAx val="638808832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="419366784"/>
+        <c:axId val="638808832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11894,7 +11984,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="419365248"/>
+        <c:crossAx val="638802944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12024,7 +12114,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12348,6 +12438,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12357,7 +12450,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12681,6 +12774,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>223000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>225000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12714,7 +12810,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13038,6 +13134,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13047,7 +13146,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13371,6 +13470,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>415926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>513881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13404,7 +13506,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13728,6 +13830,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13737,7 +13842,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14061,6 +14166,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>192926.43862532912</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>288881.23881843378</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14082,11 +14190,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="419390208"/>
-        <c:axId val="419391744"/>
+        <c:axId val="638835712"/>
+        <c:axId val="638841600"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="419390208"/>
+        <c:axId val="638835712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14096,14 +14204,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="419391744"/>
+        <c:crossAx val="638841600"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="419391744"/>
+        <c:axId val="638841600"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14114,7 +14222,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="419390208"/>
+        <c:crossAx val="638835712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14156,7 +14264,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14194,7 +14302,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14235,7 +14343,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14273,7 +14381,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14316,7 +14424,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14354,7 +14462,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14632,7 +14740,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14641,7 +14749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB110"/>
+  <dimension ref="A1:AB111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18537,6 +18645,35 @@
         <v>183014.52605583996</v>
       </c>
     </row>
+    <row r="111" spans="1:9" ht="12.75">
+      <c r="A111" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B111" s="18">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C111" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="15">
+        <v>716.84588793745536</v>
+      </c>
+      <c r="E111" s="15">
+        <v>176726.7855023171</v>
+      </c>
+      <c r="F111" s="15">
+        <v>493067.72480987286</v>
+      </c>
+      <c r="G111" s="15">
+        <v>218000</v>
+      </c>
+      <c r="H111" s="15">
+        <v>493067.72480987286</v>
+      </c>
+      <c r="I111" s="15">
+        <v>275067.72480987286</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18548,7 +18685,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24131,6 +24268,50 @@
         <v>53.107937195450262</v>
       </c>
     </row>
+    <row r="111" spans="1:14" ht="12.75">
+      <c r="A111" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B111" s="18">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C111" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="15">
+        <v>716.84588793745536</v>
+      </c>
+      <c r="E111" s="15">
+        <v>184786.12636015928</v>
+      </c>
+      <c r="F111" s="15">
+        <v>515553.28549581306</v>
+      </c>
+      <c r="G111" s="15">
+        <v>225000</v>
+      </c>
+      <c r="H111" s="15">
+        <v>515553.28549581306</v>
+      </c>
+      <c r="I111" s="15">
+        <v>290553.28549581306</v>
+      </c>
+      <c r="J111" s="21">
+        <v>0.52300000190734863</v>
+      </c>
+      <c r="K111" s="21">
+        <v>0.1742169407075714</v>
+      </c>
+      <c r="L111" s="21">
+        <v>0.52300000190734863</v>
+      </c>
+      <c r="M111" s="23">
+        <v>0.2510786513695793</v>
+      </c>
+      <c r="N111" s="21">
+        <v>69.387397039635189</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24142,7 +24323,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH110"/>
+  <dimension ref="A1:AH111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -30584,6 +30765,59 @@
         <v>64.583952119551526</v>
       </c>
     </row>
+    <row r="111" spans="1:17" ht="12.75">
+      <c r="A111" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B111" s="18">
+        <v>2.7899999618530273</v>
+      </c>
+      <c r="C111" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D111" s="15">
+        <v>716.84588793745536</v>
+      </c>
+      <c r="E111" s="15">
+        <v>184186.82646759987</v>
+      </c>
+      <c r="F111" s="15">
+        <v>513881.23881843378</v>
+      </c>
+      <c r="G111" s="15">
+        <v>225000</v>
+      </c>
+      <c r="H111" s="15">
+        <v>513881.23881843378</v>
+      </c>
+      <c r="I111" s="15">
+        <v>288881.23881843378</v>
+      </c>
+      <c r="J111" s="15">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="K111" s="15">
+        <v>2.2599999904632568</v>
+      </c>
+      <c r="L111" s="19">
+        <v>2.8289999961853027</v>
+      </c>
+      <c r="M111" s="19">
+        <v>1.6579999923706055</v>
+      </c>
+      <c r="N111" s="21">
+        <v>96.669510315522857</v>
+      </c>
+      <c r="O111" s="21">
+        <v>78.933923614270611</v>
+      </c>
+      <c r="P111" s="21">
+        <v>74.84945409521751</v>
+      </c>
+      <c r="Q111" s="21">
+        <v>87.102862652376814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel1mean.xlsx
@@ -690,7 +690,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1017,6 +1017,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1026,7 +1029,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -1353,6 +1356,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>218000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>220000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1395,7 +1401,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1722,6 +1728,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1731,7 +1740,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -2058,6 +2067,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>493067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>542783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2100,7 +2112,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2427,6 +2439,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2436,7 +2451,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2763,6 +2778,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>275067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>322783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2784,11 +2802,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578683264"/>
-        <c:axId val="578684800"/>
+        <c:axId val="399528320"/>
+        <c:axId val="399839232"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578683264"/>
+        <c:axId val="399528320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2828,14 +2846,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578684800"/>
+        <c:crossAx val="399839232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578684800"/>
+        <c:axId val="399839232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2884,7 +2902,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578683264"/>
+        <c:crossAx val="399528320"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3014,7 +3032,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3341,6 +3359,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3350,7 +3371,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -3677,6 +3698,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>218000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>220000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3710,7 +3734,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4037,6 +4061,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4046,7 +4073,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -4373,6 +4400,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>493067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>542783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4406,7 +4436,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4733,6 +4763,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4742,7 +4775,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5069,6 +5102,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>275067.72480987286</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>322783.95352470258</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5090,11 +5126,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578708224"/>
-        <c:axId val="578709760"/>
+        <c:axId val="426837504"/>
+        <c:axId val="426839424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578708224"/>
+        <c:axId val="426837504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5104,14 +5140,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="578709760"/>
+        <c:crossAx val="426839424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578709760"/>
+        <c:axId val="426839424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5122,7 +5158,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="578708224"/>
+        <c:crossAx val="426837504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5240,7 +5276,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5567,6 +5603,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5576,7 +5615,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5903,6 +5942,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5945,7 +5987,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6272,6 +6314,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6281,7 +6326,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6608,6 +6653,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>515553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>567445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6650,7 +6698,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6977,6 +7025,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6986,7 +7037,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7313,6 +7364,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>290553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>340445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7334,11 +7388,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="578741760"/>
-        <c:axId val="578743296"/>
+        <c:axId val="456520448"/>
+        <c:axId val="456522752"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="578741760"/>
+        <c:axId val="456520448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7378,14 +7432,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578743296"/>
+        <c:crossAx val="456522752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="578743296"/>
+        <c:axId val="456522752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7434,7 +7488,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="578741760"/>
+        <c:crossAx val="456520448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7564,7 +7618,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7891,6 +7945,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7900,7 +7957,7 @@
               <c:f>'model1&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8227,6 +8284,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8260,7 +8320,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8587,6 +8647,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8596,7 +8659,7 @@
               <c:f>'model1&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -8923,6 +8986,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>515553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>567445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8956,7 +9022,7 @@
               <c:f>'model1&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9283,6 +9349,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9292,7 +9361,7 @@
               <c:f>'model1&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9619,6 +9688,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>290553.28549581306</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>340445.53608854045</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9640,11 +9712,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="638392576"/>
-        <c:axId val="638398464"/>
+        <c:axId val="479673344"/>
+        <c:axId val="497464064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="638392576"/>
+        <c:axId val="479673344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9654,14 +9726,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="638398464"/>
+        <c:crossAx val="497464064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="638398464"/>
+        <c:axId val="497464064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9672,7 +9744,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="638392576"/>
+        <c:crossAx val="479673344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9790,7 +9862,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10117,6 +10189,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10126,7 +10201,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -10453,6 +10528,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10495,7 +10573,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10822,6 +10900,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10831,7 +10912,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -11158,6 +11239,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>513881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>565611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11200,7 +11284,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11527,6 +11611,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11536,7 +11623,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11863,6 +11950,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>288881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>338611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11884,11 +11974,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="638802944"/>
-        <c:axId val="638808832"/>
+        <c:axId val="610502144"/>
+        <c:axId val="610503680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="638802944"/>
+        <c:axId val="610502144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11928,14 +12018,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="638808832"/>
+        <c:crossAx val="610503680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="638808832"/>
+        <c:axId val="610503680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11984,7 +12074,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="638802944"/>
+        <c:crossAx val="610502144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12114,7 +12204,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12441,6 +12531,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12450,7 +12543,7 @@
               <c:f>'model1&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -12777,6 +12870,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>227000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12810,7 +12906,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13137,6 +13233,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13146,7 +13245,7 @@
               <c:f>'model1&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -13473,6 +13572,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>513881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>565611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13506,7 +13608,7 @@
               <c:f>'model1&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13833,6 +13935,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13842,7 +13947,7 @@
               <c:f>'model1&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14169,6 +14274,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>288881.23881843378</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>338611.67845160083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14190,11 +14298,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="638835712"/>
-        <c:axId val="638841600"/>
+        <c:axId val="497432448"/>
+        <c:axId val="497433984"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="638835712"/>
+        <c:axId val="497432448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14204,14 +14312,14 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="638841600"/>
+        <c:crossAx val="497433984"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="638841600"/>
+        <c:axId val="497433984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -14222,7 +14330,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="638835712"/>
+        <c:crossAx val="497432448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -14264,7 +14372,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14302,7 +14410,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14343,7 +14451,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14381,7 +14489,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14424,7 +14532,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14462,7 +14570,7 @@
         <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000003000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14740,7 +14848,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -14749,7 +14857,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB111"/>
+  <dimension ref="A1:AB112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -18674,6 +18782,35 @@
         <v>275067.72480987286</v>
       </c>
     </row>
+    <row r="112" spans="1:9" ht="12.75">
+      <c r="A112" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B112" s="18">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C112" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="15">
+        <v>653.59478346372339</v>
+      </c>
+      <c r="E112" s="15">
+        <v>177380.38028578082</v>
+      </c>
+      <c r="F112" s="15">
+        <v>542783.95352470258</v>
+      </c>
+      <c r="G112" s="15">
+        <v>220000</v>
+      </c>
+      <c r="H112" s="15">
+        <v>542783.95352470258</v>
+      </c>
+      <c r="I112" s="15">
+        <v>322783.95352470258</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18685,7 +18822,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -24312,6 +24449,50 @@
         <v>69.387397039635189</v>
       </c>
     </row>
+    <row r="112" spans="1:14" ht="12.75">
+      <c r="A112" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B112" s="18">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C112" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="15">
+        <v>653.59478346372339</v>
+      </c>
+      <c r="E112" s="15">
+        <v>185439.721143623</v>
+      </c>
+      <c r="F112" s="15">
+        <v>567445.53608854045</v>
+      </c>
+      <c r="G112" s="15">
+        <v>227000</v>
+      </c>
+      <c r="H112" s="15">
+        <v>567445.53608854045</v>
+      </c>
+      <c r="I112" s="15">
+        <v>340445.53608854045</v>
+      </c>
+      <c r="J112" s="21">
+        <v>0.26999998092651367</v>
+      </c>
+      <c r="K112" s="21">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="L112" s="21">
+        <v>0.26999998092651367</v>
+      </c>
+      <c r="M112" s="23">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N112" s="21">
+        <v>74.805935689687729</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24323,7 +24504,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:AH111"/>
+  <dimension ref="A1:AH112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="2" customWidth="1"/>
@@ -30818,6 +30999,59 @@
         <v>87.102862652376814</v>
       </c>
     </row>
+    <row r="112" spans="1:17" ht="12.75">
+      <c r="A112" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B112" s="18">
+        <v>3.059999942779541</v>
+      </c>
+      <c r="C112" s="22">
+        <v>2000</v>
+      </c>
+      <c r="D112" s="15">
+        <v>653.59478346372339</v>
+      </c>
+      <c r="E112" s="15">
+        <v>184840.42125106358</v>
+      </c>
+      <c r="F112" s="15">
+        <v>565611.67845160083</v>
+      </c>
+      <c r="G112" s="15">
+        <v>227000</v>
+      </c>
+      <c r="H112" s="15">
+        <v>565611.67845160083</v>
+      </c>
+      <c r="I112" s="15">
+        <v>338611.67845160083</v>
+      </c>
+      <c r="J112" s="15">
+        <v>3.2209999561309814</v>
+      </c>
+      <c r="K112" s="15">
+        <v>2.8250000476837158</v>
+      </c>
+      <c r="L112" s="19">
+        <v>3.2209999561309814</v>
+      </c>
+      <c r="M112" s="19">
+        <v>2.0439999103546143</v>
+      </c>
+      <c r="N112" s="21">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="O112" s="21">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="P112" s="21">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="Q112" s="21">
+        <v>90.125507288989468</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
